--- a/astro-site/public/dl/guia-churreria-chocolateria/temporada-franjas-y-ferias.xlsx
+++ b/astro-site/public/dl/guia-churreria-chocolateria/temporada-franjas-y-ferias.xlsx
@@ -1658,10 +1658,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="4">
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A23:H23"/>
   </mergeCells>
   <conditionalFormatting sqref="H7:H18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.3054629283128055</v>
+        <v>0.3054629283128054</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>0.3054629283128055</v>
+        <v>0.3054629283128054</v>
       </c>
       <c r="C44" s="19">
         <f>IFERROR(ABS('Parámetros'!$B$13-B44)/B44,"")</f>
@@ -3673,9 +3673,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="I18:I20"/>
     <mergeCell ref="C35:F35"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <conditionalFormatting sqref="B15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
@@ -5684,14 +5684,14 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="K22:M24"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="G16:J16"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="G16:J16"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:E12">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
@@ -6431,13 +6431,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="7">
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="K7:K9"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="E23:J23"/>
     <mergeCell ref="A25:J25"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="A23:D23"/>
   </mergeCells>
   <conditionalFormatting sqref="J7:J18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
@@ -7052,10 +7052,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="4">
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:G18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
@@ -7587,8 +7587,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="B11">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
@@ -8126,8 +8126,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="B23:D23"/>
   </mergeCells>
   <conditionalFormatting sqref="B17:D17">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
@@ -8763,19 +8763,19 @@
       </c>
       <c r="B27" s="45">
         <f>IFERROR(B25*'Parámetros'!$B$13,"")</f>
-        <v>343.6457943519062</v>
+        <v>343.6457943519061</v>
       </c>
       <c r="C27" s="45">
         <f>IFERROR(C25*'Parámetros'!$B$13,"")</f>
-        <v>230.92997380448097</v>
+        <v>230.92997380448088</v>
       </c>
       <c r="D27" s="45">
         <f>IFERROR(D25*'Parámetros'!$B$13,"")</f>
-        <v>667.1310354351674</v>
+        <v>667.1310354351672</v>
       </c>
       <c r="E27" s="45">
         <f>IFERROR(E25*'Parámetros'!$B$13,"")</f>
-        <v>256.58885978275663</v>
+        <v>256.5888597827566</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8791,11 +8791,11 @@
       </c>
       <c r="B28" s="52">
         <f>IFERROR(B20/(1+'Parámetros'!$B$34)-'Parámetros'!$B$13,"")</f>
-        <v>2.4218097989599214</v>
+        <v>2.421809798959922</v>
       </c>
       <c r="C28" s="52">
         <f>IFERROR(C20/(1+'Parámetros'!$B$34)-'Parámetros'!$B$13,"")</f>
-        <v>2.4218097989599214</v>
+        <v>2.421809798959922</v>
       </c>
       <c r="D28" s="52">
         <f>IFERROR(D20/(1+'Parámetros'!$B$34)-'Parámetros'!$B$13,"")</f>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="E28" s="52">
         <f>IFERROR(E20/(1+'Parámetros'!$B$34)-'Parámetros'!$B$13,"")</f>
-        <v>2.4218097989599214</v>
+        <v>2.421809798959922</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -8908,11 +8908,11 @@
       </c>
       <c r="B32" s="23">
         <f>IFERROR(B31/B28,"")</f>
-        <v>632.6641113099311</v>
+        <v>632.664111309931</v>
       </c>
       <c r="C32" s="23">
         <f>IFERROR(C31/C28,"")</f>
-        <v>378.5509267625389</v>
+        <v>378.55092676253884</v>
       </c>
       <c r="D32" s="23">
         <f>IFERROR(D31/D28,"")</f>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="E32" s="23">
         <f>IFERROR(E31/E28,"")</f>
-        <v>549.8595315367202</v>
+        <v>549.85953153672</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8941,11 +8941,11 @@
       </c>
       <c r="B33" s="34">
         <f>IFERROR(B32/(B8*B9),"")</f>
-        <v>12.653282226198622</v>
+        <v>12.65328222619862</v>
       </c>
       <c r="C33" s="34">
         <f>IFERROR(C32/(C8*C9),"")</f>
-        <v>10.515303521181636</v>
+        <v>10.515303521181634</v>
       </c>
       <c r="D33" s="34">
         <f>IFERROR(D32/(D8*D9),"")</f>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="E33" s="34">
         <f>IFERROR(E32/(E8*E9),"")</f>
-        <v>19.63784041202572</v>
+        <v>19.637840412025717</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8969,11 +8969,11 @@
       </c>
       <c r="B34" s="19">
         <f>IFERROR(B25/B32-1,"")</f>
-        <v>0.77819474803255</v>
+        <v>0.7781947480325502</v>
       </c>
       <c r="C34" s="19">
         <f>IFERROR(C25/C32-1,"")</f>
-        <v>0.9970892858868392</v>
+        <v>0.9970892858868396</v>
       </c>
       <c r="D34" s="19">
         <f>IFERROR(D25/D32-1,"")</f>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="E34" s="19">
         <f>IFERROR(E25/E32-1,"")</f>
-        <v>0.5276628881060035</v>
+        <v>0.5276628881060037</v>
       </c>
       <c r="F34" t="inlineStr"/>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="C35" s="47">
         <f>IFERROR(C26-C27-C31,"")</f>
-        <v>914.1098641748242</v>
+        <v>914.1098641748245</v>
       </c>
       <c r="D35" s="47">
         <f>IFERROR(D26-D27-D31,"")</f>
